--- a/output_data/charts/0500000US39159.xlsx
+++ b/output_data/charts/0500000US39159.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.803934276238039</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>5.039455413689166</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.356265356265356</c:v>
+                  <c:v>5.355840862260263</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.586274690504715</c:v>
+                  <c:v>5.5851594772647</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.975237753454154</c:v>
+                  <c:v>6.034933584353102</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.643020233496561</c:v>
+                  <c:v>6.781337346807138</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.375803460632172</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.323586596012352</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>2.506180783689504</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.690021399698819</c:v>
+                  <c:v>2.689808210492946</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.755506404939637</c:v>
+                  <c:v>2.754956310754158</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.660147137986721</c:v>
+                  <c:v>2.670073363515472</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.886396599508882</c:v>
+                  <c:v>2.888267756038128</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.954504259561356</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.279021005680302</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.015104819317912</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.458587619877942</c:v>
+                  <c:v>2.463147883975274</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.824624458575246</c:v>
+                  <c:v>2.827131866275588</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.24481129254142</c:v>
+                  <c:v>3.264751146771856</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.674770596091158</c:v>
+                  <c:v>3.808499964165413</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.273504273504273</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2420799817010408</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2336844244251025</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1902195450582547</c:v>
+                  <c:v>0.1902044698050404</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1996743771695389</c:v>
+                  <c:v>0.1980988651545632</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2018661403193971</c:v>
+                  <c:v>0.1987239828469825</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1967344945933914</c:v>
+                  <c:v>0.190640005733534</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.1924122641904045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.21993061644619</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.561282893622786</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.591503526987398</c:v>
+                  <c:v>1.589792360120463</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.635793936042761</c:v>
+                  <c:v>1.633931724995777</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.721095759315748</c:v>
+                  <c:v>1.722772573102036</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.786406651636343</c:v>
+                  <c:v>1.784562459686089</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.811185008574894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>92.13144752392208</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>88.64429166525552</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.71340255211223</c:v>
+                  <c:v>87.71120621334602</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>86.99812613276811</c:v>
+                  <c:v>87.0007217555552</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>86.19684191638257</c:v>
+                  <c:v>86.10874534941055</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>84.81267142467367</c:v>
+                  <c:v>84.5466924675697</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>83.39259073353689</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>5.356265356265356</v>
+        <v>5.355840862260263</v>
       </c>
       <c r="C12" s="2">
-        <v>2.690021399698819</v>
+        <v>2.689808210492946</v>
       </c>
       <c r="D12" s="2">
-        <v>2.458587619877942</v>
+        <v>2.463147883975274</v>
       </c>
       <c r="E12" s="2">
-        <v>0.1902195450582547</v>
+        <v>0.1902044698050404</v>
       </c>
       <c r="F12" s="2">
-        <v>1.591503526987398</v>
+        <v>1.589792360120463</v>
       </c>
       <c r="G12" s="2">
-        <v>87.71340255211223</v>
+        <v>87.71120621334602</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>5.586274690504715</v>
+        <v>5.5851594772647</v>
       </c>
       <c r="C13" s="2">
-        <v>2.755506404939637</v>
+        <v>2.754956310754158</v>
       </c>
       <c r="D13" s="2">
-        <v>2.824624458575246</v>
+        <v>2.827131866275588</v>
       </c>
       <c r="E13" s="2">
-        <v>0.1996743771695389</v>
+        <v>0.1980988651545632</v>
       </c>
       <c r="F13" s="2">
-        <v>1.635793936042761</v>
+        <v>1.633931724995777</v>
       </c>
       <c r="G13" s="2">
-        <v>86.99812613276811</v>
+        <v>87.0007217555552</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>5.975237753454154</v>
+        <v>6.034933584353102</v>
       </c>
       <c r="C14" s="2">
-        <v>2.660147137986721</v>
+        <v>2.670073363515472</v>
       </c>
       <c r="D14" s="2">
-        <v>3.24481129254142</v>
+        <v>3.264751146771856</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2018661403193971</v>
+        <v>0.1987239828469825</v>
       </c>
       <c r="F14" s="2">
-        <v>1.721095759315748</v>
+        <v>1.722772573102036</v>
       </c>
       <c r="G14" s="2">
-        <v>86.19684191638257</v>
+        <v>86.10874534941055</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>6.643020233496561</v>
+        <v>6.781337346807138</v>
       </c>
       <c r="C15" s="2">
-        <v>2.886396599508882</v>
+        <v>2.888267756038128</v>
       </c>
       <c r="D15" s="2">
-        <v>3.674770596091158</v>
+        <v>3.808499964165413</v>
       </c>
       <c r="E15" s="2">
-        <v>0.1967344945933914</v>
+        <v>0.190640005733534</v>
       </c>
       <c r="F15" s="2">
-        <v>1.786406651636343</v>
+        <v>1.784562459686089</v>
       </c>
       <c r="G15" s="2">
-        <v>84.81267142467367</v>
+        <v>84.5466924675697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>7.375803460632172</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.954504259561356</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4.273504273504273</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.1924122641904045</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.811185008574894</v>
+      </c>
+      <c r="G16" s="2">
+        <v>83.39259073353689</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39159.xlsx
+++ b/output_data/charts/0500000US39159.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.803934276238039</c:v>
+                  <c:v>2.803827386398292</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.854936818515659</c:v>
+                  <c:v>2.853376024107731</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.878896927913936</c:v>
+                  <c:v>2.879005985301917</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.005239520958084</c:v>
+                  <c:v>3.005464480874317</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.359860176267153</c:v>
+                  <c:v>3.351124170122552</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.691583630547487</c:v>
+                  <c:v>3.680959035081268</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.963957482779087</c:v>
+                  <c:v>3.91320775085011</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.211674466063826</c:v>
+                  <c:v>4.130427127715765</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.647624317034373</c:v>
+                  <c:v>4.520438891004119</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.039455413689166</c:v>
+                  <c:v>4.853529531430121</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>5.355840862260263</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.323586596012352</c:v>
+                  <c:v>2.327310155535224</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.438748799457637</c:v>
+                  <c:v>2.435257557208777</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.223569074586158</c:v>
+                  <c:v>2.225547389953785</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.320359281437125</c:v>
+                  <c:v>2.320532974025002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.35952549180023</c:v>
+                  <c:v>2.359920406151786</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.384454167739089</c:v>
+                  <c:v>2.390233139663161</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.508947680797108</c:v>
+                  <c:v>2.51884636836329</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.499912036874142</c:v>
+                  <c:v>2.51417303426177</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.489798741268414</c:v>
+                  <c:v>2.556159357585407</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.506180783689504</c:v>
+                  <c:v>2.602224181189395</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.689808210492946</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.279021005680302</c:v>
+                  <c:v>1.278972247636475</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.303176964652266</c:v>
+                  <c:v>1.301440813635936</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.390204174400546</c:v>
+                  <c:v>1.388362754754148</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.438997005988024</c:v>
+                  <c:v>1.439104723407441</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.533970473392585</c:v>
+                  <c:v>1.524928867647332</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.63069456190021</c:v>
+                  <c:v>1.621681253217622</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.588100933436449</c:v>
+                  <c:v>1.583274860114068</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.655466028640794</c:v>
+                  <c:v>1.653227226310785</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.81720727574521</c:v>
+                  <c:v>1.805060399432349</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.015104819317912</c:v>
+                  <c:v>1.991930562148234</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.463147883975274</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2420799817010408</c:v>
+                  <c:v>0.2401646843549863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2354004632681117</c:v>
+                  <c:v>0.2373104812129203</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2329633698246145</c:v>
+                  <c:v>0.2348662777483143</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2226796407185629</c:v>
+                  <c:v>0.2264391047234074</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.210107470901045</c:v>
+                  <c:v>0.2157216446915738</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2077435011214472</c:v>
+                  <c:v>0.2132823416930205</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2122263988057769</c:v>
+                  <c:v>0.2141019413108796</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2075929770240315</c:v>
+                  <c:v>0.2077537941476813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2351476588975724</c:v>
+                  <c:v>0.2370980582188225</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2336844244251025</c:v>
+                  <c:v>0.2356411473520038</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.1902044698050404</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.21993061644619</c:v>
+                  <c:v>1.219884111009454</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.244797649761775</c:v>
+                  <c:v>1.239288068556361</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.299291639834842</c:v>
+                  <c:v>1.28418819607546</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.366017964071856</c:v>
+                  <c:v>1.341792050303166</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.340597225837641</c:v>
+                  <c:v>1.314786231008127</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.33102915762768</c:v>
+                  <c:v>1.301757740678091</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.368680419416917</c:v>
+                  <c:v>1.34758280707436</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.460187889236832</c:v>
+                  <c:v>1.445473432163104</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.537104917352514</c:v>
+                  <c:v>1.498736630784673</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.561282893622786</c:v>
+                  <c:v>1.518953007391334</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.589792360120463</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>92.13144752392208</c:v>
+                  <c:v>92.12984141506557</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>91.92293930434455</c:v>
+                  <c:v>91.93332705527828</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91.9750748134399</c:v>
+                  <c:v>91.98802939616637</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91.64670658682634</c:v>
+                  <c:v>91.66666666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>91.19593916180135</c:v>
+                  <c:v>91.23351868037864</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>90.7544949810641</c:v>
+                  <c:v>90.79208648966683</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>90.35808708476466</c:v>
+                  <c:v>90.4229862722873</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>89.96516660216038</c:v>
+                  <c:v>90.04894538540088</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>89.27311708970191</c:v>
+                  <c:v>89.38250666297462</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.64429166525552</c:v>
+                  <c:v>88.7977215704889</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>87.71120621334602</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>2.803934276238039</v>
+        <v>2.803827386398292</v>
       </c>
       <c r="C2" s="2">
-        <v>2.323586596012352</v>
+        <v>2.327310155535224</v>
       </c>
       <c r="D2" s="2">
-        <v>1.279021005680302</v>
+        <v>1.278972247636475</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2420799817010408</v>
+        <v>0.2401646843549863</v>
       </c>
       <c r="F2" s="2">
-        <v>1.21993061644619</v>
+        <v>1.219884111009454</v>
       </c>
       <c r="G2" s="2">
-        <v>92.13144752392208</v>
+        <v>92.12984141506557</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>2.854936818515659</v>
+        <v>2.853376024107731</v>
       </c>
       <c r="C3" s="2">
-        <v>2.438748799457637</v>
+        <v>2.435257557208777</v>
       </c>
       <c r="D3" s="2">
-        <v>1.303176964652266</v>
+        <v>1.301440813635936</v>
       </c>
       <c r="E3" s="2">
-        <v>0.2354004632681117</v>
+        <v>0.2373104812129203</v>
       </c>
       <c r="F3" s="2">
-        <v>1.244797649761775</v>
+        <v>1.239288068556361</v>
       </c>
       <c r="G3" s="2">
-        <v>91.92293930434455</v>
+        <v>91.93332705527828</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>2.878896927913936</v>
+        <v>2.879005985301917</v>
       </c>
       <c r="C4" s="2">
-        <v>2.223569074586158</v>
+        <v>2.225547389953785</v>
       </c>
       <c r="D4" s="2">
-        <v>1.390204174400546</v>
+        <v>1.388362754754148</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2329633698246145</v>
+        <v>0.2348662777483143</v>
       </c>
       <c r="F4" s="2">
-        <v>1.299291639834842</v>
+        <v>1.28418819607546</v>
       </c>
       <c r="G4" s="2">
-        <v>91.9750748134399</v>
+        <v>91.98802939616637</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>3.005239520958084</v>
+        <v>3.005464480874317</v>
       </c>
       <c r="C5" s="2">
-        <v>2.320359281437125</v>
+        <v>2.320532974025002</v>
       </c>
       <c r="D5" s="2">
-        <v>1.438997005988024</v>
+        <v>1.439104723407441</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2226796407185629</v>
+        <v>0.2264391047234074</v>
       </c>
       <c r="F5" s="2">
-        <v>1.366017964071856</v>
+        <v>1.341792050303166</v>
       </c>
       <c r="G5" s="2">
-        <v>91.64670658682634</v>
+        <v>91.66666666666666</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>3.359860176267153</v>
+        <v>3.351124170122552</v>
       </c>
       <c r="C6" s="2">
-        <v>2.35952549180023</v>
+        <v>2.359920406151786</v>
       </c>
       <c r="D6" s="2">
-        <v>1.533970473392585</v>
+        <v>1.524928867647332</v>
       </c>
       <c r="E6" s="2">
-        <v>0.210107470901045</v>
+        <v>0.2157216446915738</v>
       </c>
       <c r="F6" s="2">
-        <v>1.340597225837641</v>
+        <v>1.314786231008127</v>
       </c>
       <c r="G6" s="2">
-        <v>91.19593916180135</v>
+        <v>91.23351868037864</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>3.691583630547487</v>
+        <v>3.680959035081268</v>
       </c>
       <c r="C7" s="2">
-        <v>2.384454167739089</v>
+        <v>2.390233139663161</v>
       </c>
       <c r="D7" s="2">
-        <v>1.63069456190021</v>
+        <v>1.621681253217622</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2077435011214472</v>
+        <v>0.2132823416930205</v>
       </c>
       <c r="F7" s="2">
-        <v>1.33102915762768</v>
+        <v>1.301757740678091</v>
       </c>
       <c r="G7" s="2">
-        <v>90.7544949810641</v>
+        <v>90.79208648966683</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>3.963957482779087</v>
+        <v>3.91320775085011</v>
       </c>
       <c r="C8" s="2">
-        <v>2.508947680797108</v>
+        <v>2.51884636836329</v>
       </c>
       <c r="D8" s="2">
-        <v>1.588100933436449</v>
+        <v>1.583274860114068</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2122263988057769</v>
+        <v>0.2141019413108796</v>
       </c>
       <c r="F8" s="2">
-        <v>1.368680419416917</v>
+        <v>1.34758280707436</v>
       </c>
       <c r="G8" s="2">
-        <v>90.35808708476466</v>
+        <v>90.4229862722873</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>4.211674466063826</v>
+        <v>4.130427127715765</v>
       </c>
       <c r="C9" s="2">
-        <v>2.499912036874142</v>
+        <v>2.51417303426177</v>
       </c>
       <c r="D9" s="2">
-        <v>1.655466028640794</v>
+        <v>1.653227226310785</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2075929770240315</v>
+        <v>0.2077537941476813</v>
       </c>
       <c r="F9" s="2">
-        <v>1.460187889236832</v>
+        <v>1.445473432163104</v>
       </c>
       <c r="G9" s="2">
-        <v>89.96516660216038</v>
+        <v>90.04894538540088</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>4.647624317034373</v>
+        <v>4.520438891004119</v>
       </c>
       <c r="C10" s="2">
-        <v>2.489798741268414</v>
+        <v>2.556159357585407</v>
       </c>
       <c r="D10" s="2">
-        <v>1.81720727574521</v>
+        <v>1.805060399432349</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2351476588975724</v>
+        <v>0.2370980582188225</v>
       </c>
       <c r="F10" s="2">
-        <v>1.537104917352514</v>
+        <v>1.498736630784673</v>
       </c>
       <c r="G10" s="2">
-        <v>89.27311708970191</v>
+        <v>89.38250666297462</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>5.039455413689166</v>
+        <v>4.853529531430121</v>
       </c>
       <c r="C11" s="2">
-        <v>2.506180783689504</v>
+        <v>2.602224181189395</v>
       </c>
       <c r="D11" s="2">
-        <v>2.015104819317912</v>
+        <v>1.991930562148234</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2336844244251025</v>
+        <v>0.2356411473520038</v>
       </c>
       <c r="F11" s="2">
-        <v>1.561282893622786</v>
+        <v>1.518953007391334</v>
       </c>
       <c r="G11" s="2">
-        <v>88.64429166525552</v>
+        <v>88.7977215704889</v>
       </c>
     </row>
     <row r="12" spans="1:7">
